--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/185.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/185.xlsx
@@ -426,13 +426,13 @@
         <v>4.957978298298295</v>
       </c>
       <c r="E2">
-        <v>-14.75954419805741</v>
+        <v>-15.48239733305778</v>
       </c>
       <c r="F2">
-        <v>-1.331903101349735</v>
+        <v>-1.752537299715087</v>
       </c>
       <c r="G2">
-        <v>-9.89577793920051</v>
+        <v>-8.245083654045729</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>4.663030237250933</v>
       </c>
       <c r="E3">
-        <v>-13.49878080652992</v>
+        <v>-15.03521958174835</v>
       </c>
       <c r="F3">
-        <v>-1.221960522915379</v>
+        <v>-2.095097870366586</v>
       </c>
       <c r="G3">
-        <v>-10.37844554718963</v>
+        <v>-7.376638174365335</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>4.433513667769104</v>
       </c>
       <c r="E4">
-        <v>-15.57139996120453</v>
+        <v>-14.83822190546667</v>
       </c>
       <c r="F4">
-        <v>-1.33724275762818</v>
+        <v>-2.132077847962362</v>
       </c>
       <c r="G4">
-        <v>-8.963846127713513</v>
+        <v>-6.758552701092326</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>4.30103053895534</v>
       </c>
       <c r="E5">
-        <v>-17.38326505404348</v>
+        <v>-15.90462772105896</v>
       </c>
       <c r="F5">
-        <v>-1.971950287164204</v>
+        <v>-1.775856670471296</v>
       </c>
       <c r="G5">
-        <v>-8.494976873532075</v>
+        <v>-7.062927568518458</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.267201414189302</v>
       </c>
       <c r="E6">
-        <v>-16.05639499895202</v>
+        <v>-16.30342325607044</v>
       </c>
       <c r="F6">
-        <v>-1.354752787788556</v>
+        <v>-1.550706410390391</v>
       </c>
       <c r="G6">
-        <v>-9.411388847530967</v>
+        <v>-7.757235042287648</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.336622007663953</v>
       </c>
       <c r="E7">
-        <v>-15.87184156924342</v>
+        <v>-16.5797009268044</v>
       </c>
       <c r="F7">
-        <v>-1.866400541066893</v>
+        <v>-1.919999225497633</v>
       </c>
       <c r="G7">
-        <v>-8.471726912209773</v>
+        <v>-6.482575693302063</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.495829201187237</v>
       </c>
       <c r="E8">
-        <v>-18.05741445109136</v>
+        <v>-16.87596728180822</v>
       </c>
       <c r="F8">
-        <v>-1.631573292986484</v>
+        <v>-1.865249938744405</v>
       </c>
       <c r="G8">
-        <v>-8.34969027199562</v>
+        <v>-6.421376948463095</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.736868001283693</v>
       </c>
       <c r="E9">
-        <v>-17.23829501563593</v>
+        <v>-18.0405549423608</v>
       </c>
       <c r="F9">
-        <v>-1.531346635819563</v>
+        <v>-1.850940720228446</v>
       </c>
       <c r="G9">
-        <v>-9.344068903989887</v>
+        <v>-6.192605009517299</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>5.047800884763279</v>
       </c>
       <c r="E10">
-        <v>-18.35651563082398</v>
+        <v>-17.87499393264038</v>
       </c>
       <c r="F10">
-        <v>-1.231347582323903</v>
+        <v>-2.03914165230748</v>
       </c>
       <c r="G10">
-        <v>-7.149932015836044</v>
+        <v>-4.953782315994324</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>5.409493684912914</v>
       </c>
       <c r="E11">
-        <v>-18.3714641235233</v>
+        <v>-18.94579689649411</v>
       </c>
       <c r="F11">
-        <v>-1.229937701004338</v>
+        <v>-2.070220340525712</v>
       </c>
       <c r="G11">
-        <v>-7.133627579055134</v>
+        <v>-5.602735315875498</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.793748893266121</v>
       </c>
       <c r="E12">
-        <v>-19.85500579385813</v>
+        <v>-18.67018943991328</v>
       </c>
       <c r="F12">
-        <v>-0.8905572328121862</v>
+        <v>-2.238402945948692</v>
       </c>
       <c r="G12">
-        <v>-6.461077010570035</v>
+        <v>-4.70211133355339</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>6.174506590907875</v>
       </c>
       <c r="E13">
-        <v>-18.98980913537466</v>
+        <v>-19.50743182834741</v>
       </c>
       <c r="F13">
-        <v>-1.173224355139073</v>
+        <v>-1.892786527948266</v>
       </c>
       <c r="G13">
-        <v>-5.625492005912449</v>
+        <v>-4.334955280520519</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>6.528549143994973</v>
       </c>
       <c r="E14">
-        <v>-19.23105905965929</v>
+        <v>-19.98200231892924</v>
       </c>
       <c r="F14">
-        <v>-0.9881993836823724</v>
+        <v>-1.83239191734496</v>
       </c>
       <c r="G14">
-        <v>-4.951279543566636</v>
+        <v>-3.841803174808526</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.829091804969281</v>
       </c>
       <c r="E15">
-        <v>-21.98228815827934</v>
+        <v>-20.56833554802037</v>
       </c>
       <c r="F15">
-        <v>-1.552536273983175</v>
+        <v>-1.579208047618513</v>
       </c>
       <c r="G15">
-        <v>-5.308629760712186</v>
+        <v>-3.586967310832047</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>7.056319494332589</v>
       </c>
       <c r="E16">
-        <v>-21.56751616696879</v>
+        <v>-21.61540477959991</v>
       </c>
       <c r="F16">
-        <v>-0.9421711489458179</v>
+        <v>-1.73086058151863</v>
       </c>
       <c r="G16">
-        <v>-4.973417161587742</v>
+        <v>-2.580717062533952</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>7.201650960566885</v>
       </c>
       <c r="E17">
-        <v>-21.3985542732686</v>
+        <v>-21.87997181655003</v>
       </c>
       <c r="F17">
-        <v>-1.402317644057304</v>
+        <v>-1.405566501011084</v>
       </c>
       <c r="G17">
-        <v>-4.575820642321272</v>
+        <v>-2.139619974881459</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>7.26428083774015</v>
       </c>
       <c r="E18">
-        <v>-23.24277078441835</v>
+        <v>-23.47997225294012</v>
       </c>
       <c r="F18">
-        <v>-0.9692322552604721</v>
+        <v>-1.937486889738133</v>
       </c>
       <c r="G18">
-        <v>-3.129165210388392</v>
+        <v>-1.611753488644668</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>7.242385112893699</v>
       </c>
       <c r="E19">
-        <v>-23.30459351157106</v>
+        <v>-23.72091424099223</v>
       </c>
       <c r="F19">
-        <v>-0.6338511448890363</v>
+        <v>-1.619421143187415</v>
       </c>
       <c r="G19">
-        <v>-4.26858215300367</v>
+        <v>-1.871045346917006</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>7.140327051526233</v>
       </c>
       <c r="E20">
-        <v>-23.79207468154876</v>
+        <v>-23.77635181979413</v>
       </c>
       <c r="F20">
-        <v>-0.7895982988611909</v>
+        <v>-1.204395820506418</v>
       </c>
       <c r="G20">
-        <v>-3.795094687794948</v>
+        <v>-1.771715738556713</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.967457825572286</v>
       </c>
       <c r="E21">
-        <v>-24.47433910401839</v>
+        <v>-24.93265237291268</v>
       </c>
       <c r="F21">
-        <v>-0.4265339782555984</v>
+        <v>-1.07259179794478</v>
       </c>
       <c r="G21">
-        <v>-3.70033363227885</v>
+        <v>-1.5019559352892</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.734480784280187</v>
       </c>
       <c r="E22">
-        <v>-24.15499564547148</v>
+        <v>-25.17618464809718</v>
       </c>
       <c r="F22">
-        <v>0.01225472010950813</v>
+        <v>-0.8205585305408224</v>
       </c>
       <c r="G22">
-        <v>-2.670237524461384</v>
+        <v>-1.171219193733852</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.44879084477856</v>
       </c>
       <c r="E23">
-        <v>-25.5731733219796</v>
+        <v>-25.24892552608238</v>
       </c>
       <c r="F23">
-        <v>-0.5758886209803492</v>
+        <v>-0.7445955829693022</v>
       </c>
       <c r="G23">
-        <v>-3.298685005272312</v>
+        <v>-1.386053735959316</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>6.119622098720876</v>
       </c>
       <c r="E24">
-        <v>-26.52548423494863</v>
+        <v>-25.2324645230645</v>
       </c>
       <c r="F24">
-        <v>-0.09221069305753751</v>
+        <v>-0.3593848598498648</v>
       </c>
       <c r="G24">
-        <v>-3.327417230007647</v>
+        <v>-1.683357278113565</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.761234694993657</v>
       </c>
       <c r="E25">
-        <v>-25.06413208725138</v>
+        <v>-25.98539125394982</v>
       </c>
       <c r="F25">
-        <v>-0.5832561206608481</v>
+        <v>-0.8325466635941369</v>
       </c>
       <c r="G25">
-        <v>-3.171222380919293</v>
+        <v>-1.66616561512813</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.383600198013865</v>
       </c>
       <c r="E26">
-        <v>-26.87404540779302</v>
+        <v>-26.08810610139179</v>
       </c>
       <c r="F26">
-        <v>-0.2019875980113336</v>
+        <v>-0.4155440279226573</v>
       </c>
       <c r="G26">
-        <v>-1.870886440731121</v>
+        <v>-1.716482596779512</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.993846735289084</v>
       </c>
       <c r="E27">
-        <v>-27.46024731113794</v>
+        <v>-26.23820690085004</v>
       </c>
       <c r="F27">
-        <v>-0.5313804404279319</v>
+        <v>-0.483238212079433</v>
       </c>
       <c r="G27">
-        <v>-3.244358952972872</v>
+        <v>-2.317290332883065</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.596652673333518</v>
       </c>
       <c r="E28">
-        <v>-26.52053914133225</v>
+        <v>-25.90655504995028</v>
       </c>
       <c r="F28">
-        <v>0.1740514412243076</v>
+        <v>-0.7046782145631996</v>
       </c>
       <c r="G28">
-        <v>-3.443984848990925</v>
+        <v>-1.942215454920257</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.203196349575136</v>
       </c>
       <c r="E29">
-        <v>-26.68084259272977</v>
+        <v>-26.55166334318697</v>
       </c>
       <c r="F29">
-        <v>0.1035383227958053</v>
+        <v>-0.6096329955007899</v>
       </c>
       <c r="G29">
-        <v>-2.247805292559302</v>
+        <v>-2.342586211348636</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.816292223431639</v>
       </c>
       <c r="E30">
-        <v>-26.60747678533151</v>
+        <v>-26.19019601942071</v>
       </c>
       <c r="F30">
-        <v>0.06969620092183425</v>
+        <v>-0.4335866983230334</v>
       </c>
       <c r="G30">
-        <v>-2.98790423222769</v>
+        <v>-2.744850599825478</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.436197259505328</v>
       </c>
       <c r="E31">
-        <v>-25.28740396972556</v>
+        <v>-25.40901161072754</v>
       </c>
       <c r="F31">
-        <v>0.2735830981402794</v>
+        <v>-0.5748755276467254</v>
       </c>
       <c r="G31">
-        <v>-4.343996380388268</v>
+        <v>-2.349501940980174</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.063643175401393</v>
       </c>
       <c r="E32">
-        <v>-25.84695127506133</v>
+        <v>-25.56504471113583</v>
       </c>
       <c r="F32">
-        <v>-0.06931710314636758</v>
+        <v>-0.3528175630804704</v>
       </c>
       <c r="G32">
-        <v>-4.213504606866816</v>
+        <v>-2.35229273086978</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.701799108056739</v>
       </c>
       <c r="E33">
-        <v>-25.5324985684427</v>
+        <v>-24.73964881070577</v>
       </c>
       <c r="F33">
-        <v>-0.9150313477278976</v>
+        <v>-0.466327091551281</v>
       </c>
       <c r="G33">
-        <v>-2.550097826841233</v>
+        <v>-2.996405713172539</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.349228646582769</v>
       </c>
       <c r="E34">
-        <v>-24.50908155660523</v>
+        <v>-24.65392479774057</v>
       </c>
       <c r="F34">
-        <v>-0.4115554388781777</v>
+        <v>-0.3234395131401859</v>
       </c>
       <c r="G34">
-        <v>-3.482013085600533</v>
+        <v>-3.100459470017372</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.002052596521473</v>
       </c>
       <c r="E35">
-        <v>-25.13632954835567</v>
+        <v>-24.95531285684706</v>
       </c>
       <c r="F35">
-        <v>0.14192652497634</v>
+        <v>-0.3384503588463157</v>
       </c>
       <c r="G35">
-        <v>-4.850062924248959</v>
+        <v>-2.631941133663095</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.660781031585076</v>
       </c>
       <c r="E36">
-        <v>-23.74780884812379</v>
+        <v>-24.25916866154393</v>
       </c>
       <c r="F36">
-        <v>0.1041877628396001</v>
+        <v>-0.4196577004449597</v>
       </c>
       <c r="G36">
-        <v>-4.036565879429388</v>
+        <v>-3.099300779078626</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.325781815605383</v>
       </c>
       <c r="E37">
-        <v>-23.86484725885202</v>
+        <v>-24.66701661609675</v>
       </c>
       <c r="F37">
-        <v>-0.5586627208391335</v>
+        <v>-0.4841775807142076</v>
       </c>
       <c r="G37">
-        <v>-4.526281638871618</v>
+        <v>-3.076683131954326</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.9970536953484638</v>
       </c>
       <c r="E38">
-        <v>-23.80264413988267</v>
+        <v>-22.77534169734662</v>
       </c>
       <c r="F38">
-        <v>0.482376415485506</v>
+        <v>-0.4067467661049266</v>
       </c>
       <c r="G38">
-        <v>-4.903567961254659</v>
+        <v>-3.636734741923911</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.6723719377540648</v>
       </c>
       <c r="E39">
-        <v>-24.46336208302379</v>
+        <v>-22.68885237227412</v>
       </c>
       <c r="F39">
-        <v>0.2266005841556998</v>
+        <v>-0.01490661866088486</v>
       </c>
       <c r="G39">
-        <v>-5.058842478683095</v>
+        <v>-2.349306618793357</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.3560678834692042</v>
       </c>
       <c r="E40">
-        <v>-21.57390584379361</v>
+        <v>-22.70895426839417</v>
       </c>
       <c r="F40">
-        <v>0.08219792176488439</v>
+        <v>-0.5273636868917571</v>
       </c>
       <c r="G40">
-        <v>-4.284956111240906</v>
+        <v>-3.143221786748137</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.05105598746866034</v>
       </c>
       <c r="E41">
-        <v>-21.58587460059589</v>
+        <v>-21.68954948452749</v>
       </c>
       <c r="F41">
-        <v>0.1514080182687831</v>
+        <v>-0.1178751719310718</v>
       </c>
       <c r="G41">
-        <v>-4.567014591186811</v>
+        <v>-2.812498287374946</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.2391556513123343</v>
       </c>
       <c r="E42">
-        <v>-23.19196583452629</v>
+        <v>-22.04706345048505</v>
       </c>
       <c r="F42">
-        <v>0.1210293005059168</v>
+        <v>0.05596186938341845</v>
       </c>
       <c r="G42">
-        <v>-3.829722994135725</v>
+        <v>-2.718309956237141</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.5120689386214788</v>
       </c>
       <c r="E43">
-        <v>-22.11718234201982</v>
+        <v>-20.6781646281284</v>
       </c>
       <c r="F43">
-        <v>-0.3123741813735901</v>
+        <v>-0.2981279187802442</v>
       </c>
       <c r="G43">
-        <v>-5.830179726060046</v>
+        <v>-3.182700042303946</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.7609907125449538</v>
       </c>
       <c r="E44">
-        <v>-22.49585333854121</v>
+        <v>-21.38927090155288</v>
       </c>
       <c r="F44">
-        <v>-0.3412817186290845</v>
+        <v>-0.08953092450948112</v>
       </c>
       <c r="G44">
-        <v>-3.954878168247872</v>
+        <v>-2.776244503174387</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.9807700715184977</v>
       </c>
       <c r="E45">
-        <v>-20.81694877104147</v>
+        <v>-19.72765151934042</v>
       </c>
       <c r="F45">
-        <v>0.2843129411087414</v>
+        <v>-0.07929064667607363</v>
       </c>
       <c r="G45">
-        <v>-4.522534101321163</v>
+        <v>-3.033258706115705</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.167548189459205</v>
       </c>
       <c r="E46">
-        <v>-19.98771272465291</v>
+        <v>-19.4480318347888</v>
       </c>
       <c r="F46">
-        <v>-0.5218914918288635</v>
+        <v>-0.1940526666599171</v>
       </c>
       <c r="G46">
-        <v>-5.588609218059428</v>
+        <v>-3.339934402691631</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.317803436768583</v>
       </c>
       <c r="E47">
-        <v>-18.98264056102051</v>
+        <v>-19.12506106856175</v>
       </c>
       <c r="F47">
-        <v>0.4546310776961393</v>
+        <v>-0.2494671324375929</v>
       </c>
       <c r="G47">
-        <v>-4.256147743958168</v>
+        <v>-3.076699684682022</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.428543092705867</v>
       </c>
       <c r="E48">
-        <v>-20.67118624968258</v>
+        <v>-19.58150860616488</v>
       </c>
       <c r="F48">
-        <v>0.1689544965948822</v>
+        <v>0.183019346727015</v>
       </c>
       <c r="G48">
-        <v>-6.385752167914998</v>
+        <v>-3.252598900820118</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.498566076285623</v>
       </c>
       <c r="E49">
-        <v>-19.99158004145546</v>
+        <v>-18.83561459541348</v>
       </c>
       <c r="F49">
-        <v>-0.1424520044047303</v>
+        <v>0.07234946171300106</v>
       </c>
       <c r="G49">
-        <v>-4.927344299317705</v>
+        <v>-2.985348491071373</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.52901851383015</v>
       </c>
       <c r="E50">
-        <v>-17.19997506858302</v>
+        <v>-19.04439988953712</v>
       </c>
       <c r="F50">
-        <v>-0.3186308403669348</v>
+        <v>-0.003980452617959377</v>
       </c>
       <c r="G50">
-        <v>-6.148412537113568</v>
+        <v>-3.281311262282217</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.521811504987795</v>
       </c>
       <c r="E51">
-        <v>-18.75713161238654</v>
+        <v>-18.41822061765249</v>
       </c>
       <c r="F51">
-        <v>-0.2083063845598882</v>
+        <v>-0.260642637068761</v>
       </c>
       <c r="G51">
-        <v>-6.111850872177857</v>
+        <v>-3.804029850205441</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.480178257457021</v>
       </c>
       <c r="E52">
-        <v>-16.44782723522703</v>
+        <v>-17.31195517384469</v>
       </c>
       <c r="F52">
-        <v>0.1803992206319602</v>
+        <v>-0.2437911589936106</v>
       </c>
       <c r="G52">
-        <v>-4.794962204293329</v>
+        <v>-3.976125249518915</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.408720017235523</v>
       </c>
       <c r="E53">
-        <v>-17.16301366373242</v>
+        <v>-15.97634063544442</v>
       </c>
       <c r="F53">
-        <v>-0.2333189382874193</v>
+        <v>-0.0444901037170636</v>
       </c>
       <c r="G53">
-        <v>-6.532366298212701</v>
+        <v>-3.032593286462312</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.312879884370518</v>
       </c>
       <c r="E54">
-        <v>-16.00285485075933</v>
+        <v>-16.44299082498684</v>
       </c>
       <c r="F54">
-        <v>0.2775981949416486</v>
+        <v>-0.3042860020526558</v>
       </c>
       <c r="G54">
-        <v>-6.336123779735783</v>
+        <v>-3.801500593413438</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.198875580039392</v>
       </c>
       <c r="E55">
-        <v>-15.83057811408553</v>
+        <v>-16.50229572059129</v>
       </c>
       <c r="F55">
-        <v>0.06567447718124265</v>
+        <v>-0.03697349790406088</v>
       </c>
       <c r="G55">
-        <v>-5.243868868872962</v>
+        <v>-3.695294981968079</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.072784838865287</v>
       </c>
       <c r="E56">
-        <v>-15.49107388925648</v>
+        <v>-16.2172645096005</v>
       </c>
       <c r="F56">
-        <v>0.05376172556158296</v>
+        <v>-0.5021846313162632</v>
       </c>
       <c r="G56">
-        <v>-6.850327644532002</v>
+        <v>-4.801738891012216</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.940046613035957</v>
       </c>
       <c r="E57">
-        <v>-16.8096568369139</v>
+        <v>-15.80754629528252</v>
       </c>
       <c r="F57">
-        <v>0.01313775976089241</v>
+        <v>-0.237166704873423</v>
       </c>
       <c r="G57">
-        <v>-6.536617038685125</v>
+        <v>-4.188149138581537</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.8052996770554506</v>
       </c>
       <c r="E58">
-        <v>-16.1769973187243</v>
+        <v>-15.64526842921765</v>
       </c>
       <c r="F58">
-        <v>0.1600528604843987</v>
+        <v>-0.4154098324034038</v>
       </c>
       <c r="G58">
-        <v>-6.003245115216527</v>
+        <v>-3.436569226982957</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.6738491330341668</v>
       </c>
       <c r="E59">
-        <v>-14.89819701522426</v>
+        <v>-15.52721111183769</v>
       </c>
       <c r="F59">
-        <v>-0.3241858721701082</v>
+        <v>-0.4463882881658969</v>
       </c>
       <c r="G59">
-        <v>-6.449360989906554</v>
+        <v>-4.164783308165362</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.5492070844942856</v>
       </c>
       <c r="E60">
-        <v>-14.37691531525331</v>
+        <v>-15.7043333156997</v>
       </c>
       <c r="F60">
-        <v>-0.843329522076378</v>
+        <v>-0.2460890501689765</v>
       </c>
       <c r="G60">
-        <v>-6.129800650091785</v>
+        <v>-4.848563247119668</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.4334552024493698</v>
       </c>
       <c r="E61">
-        <v>-15.76885954183499</v>
+        <v>-14.77032196619566</v>
       </c>
       <c r="F61">
-        <v>-0.263282643981483</v>
+        <v>-0.02894744613833648</v>
       </c>
       <c r="G61">
-        <v>-6.033814692726157</v>
+        <v>-4.977949298431004</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.3282342612043247</v>
       </c>
       <c r="E62">
-        <v>-15.3962114157438</v>
+        <v>-14.33522618353869</v>
       </c>
       <c r="F62">
-        <v>0.198529697977033</v>
+        <v>-0.3075390008434494</v>
       </c>
       <c r="G62">
-        <v>-6.85347266279431</v>
+        <v>-5.126159111678636</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.2348542404772322</v>
       </c>
       <c r="E63">
-        <v>-13.90503020975802</v>
+        <v>-14.27675452715165</v>
       </c>
       <c r="F63">
-        <v>-0.3463140506010914</v>
+        <v>-0.2794656295625741</v>
       </c>
       <c r="G63">
-        <v>-6.984480881419889</v>
+        <v>-4.6549128858</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.1534351274889142</v>
       </c>
       <c r="E64">
-        <v>-14.24479255760552</v>
+        <v>-14.45282159656988</v>
       </c>
       <c r="F64">
-        <v>-0.1217610434176043</v>
+        <v>-0.6308955299958476</v>
       </c>
       <c r="G64">
-        <v>-6.072465311897147</v>
+        <v>-5.411372541523466</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.0827495189572325</v>
       </c>
       <c r="E65">
-        <v>-14.82310133075506</v>
+        <v>-14.46524320077292</v>
       </c>
       <c r="F65">
-        <v>-0.5605215772910156</v>
+        <v>-0.4600190737789628</v>
       </c>
       <c r="G65">
-        <v>-7.902892424924501</v>
+        <v>-5.04533545288287</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.02192276096777887</v>
       </c>
       <c r="E66">
-        <v>-14.90311040952258</v>
+        <v>-14.13177543179609</v>
       </c>
       <c r="F66">
-        <v>-0.6964840042147069</v>
+        <v>-0.4428155395576227</v>
       </c>
       <c r="G66">
-        <v>-7.128231389826122</v>
+        <v>-5.224230712734006</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.03091792191105055</v>
       </c>
       <c r="E67">
-        <v>-14.45526244406001</v>
+        <v>-13.30148425096374</v>
       </c>
       <c r="F67">
-        <v>-0.750578880719723</v>
+        <v>-0.7683631004904256</v>
       </c>
       <c r="G67">
-        <v>-6.846739013167432</v>
+        <v>-5.03306657111433</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.07783876118022892</v>
       </c>
       <c r="E68">
-        <v>-13.48758641878296</v>
+        <v>-14.0901632841396</v>
       </c>
       <c r="F68">
-        <v>-0.73750227289913</v>
+        <v>-0.8713921245810169</v>
       </c>
       <c r="G68">
-        <v>-8.604853879980485</v>
+        <v>-4.575310818308225</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.1223067875908498</v>
       </c>
       <c r="E69">
-        <v>-14.17679299190634</v>
+        <v>-13.40677127164207</v>
       </c>
       <c r="F69">
-        <v>-0.5495573063475614</v>
+        <v>-0.5229675410851</v>
       </c>
       <c r="G69">
-        <v>-7.15595058762644</v>
+        <v>-5.021469730090264</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.1670568693667304</v>
       </c>
       <c r="E70">
-        <v>-12.92910330483899</v>
+        <v>-14.13073841124833</v>
       </c>
       <c r="F70">
-        <v>-0.6497143806526468</v>
+        <v>-0.7210525530143375</v>
       </c>
       <c r="G70">
-        <v>-7.061586797575053</v>
+        <v>-5.221158526473562</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.2152710285499649</v>
       </c>
       <c r="E71">
-        <v>-15.28317164756433</v>
+        <v>-12.94410613922641</v>
       </c>
       <c r="F71">
-        <v>-0.5428317914042322</v>
+        <v>-0.5937101172841778</v>
       </c>
       <c r="G71">
-        <v>-7.405939812933425</v>
+        <v>-5.038479313071038</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.2700094235325087</v>
       </c>
       <c r="E72">
-        <v>-14.83648297144773</v>
+        <v>-13.40813434231838</v>
       </c>
       <c r="F72">
-        <v>-0.8594048198951052</v>
+        <v>-0.7411007008968911</v>
       </c>
       <c r="G72">
-        <v>-6.560999206581857</v>
+        <v>-4.53731237660847</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.3349656338772125</v>
       </c>
       <c r="E73">
-        <v>-11.67449410948793</v>
+        <v>-13.68169945712175</v>
       </c>
       <c r="F73">
-        <v>-0.8497071227105314</v>
+        <v>-0.57727365127783</v>
       </c>
       <c r="G73">
-        <v>-6.939675958091392</v>
+        <v>-4.399262627620861</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.4126488632089806</v>
       </c>
       <c r="E74">
-        <v>-13.85461018015662</v>
+        <v>-14.55337183343619</v>
       </c>
       <c r="F74">
-        <v>-0.7206499664565769</v>
+        <v>-1.356735899350858</v>
       </c>
       <c r="G74">
-        <v>-6.571748547947871</v>
+        <v>-4.578723990759213</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.5039860219227548</v>
       </c>
       <c r="E75">
-        <v>-13.18446395413152</v>
+        <v>-15.28783144731822</v>
       </c>
       <c r="F75">
-        <v>-0.8089655287386434</v>
+        <v>-1.055168746361698</v>
       </c>
       <c r="G75">
-        <v>-6.4593290425253</v>
+        <v>-4.257081317800242</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.6096684305771042</v>
       </c>
       <c r="E76">
-        <v>-15.6697991729172</v>
+        <v>-15.20827068747746</v>
       </c>
       <c r="F76">
-        <v>-0.7766235802311422</v>
+        <v>-1.032159185014137</v>
       </c>
       <c r="G76">
-        <v>-6.830566998208092</v>
+        <v>-4.3628400055978</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.7299110414943113</v>
       </c>
       <c r="E77">
-        <v>-15.59140223089641</v>
+        <v>-14.92834306669332</v>
       </c>
       <c r="F77">
-        <v>-1.222590082141507</v>
+        <v>-1.305865028777538</v>
       </c>
       <c r="G77">
-        <v>-6.006327233113588</v>
+        <v>-4.276951212126948</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.863616321924946</v>
       </c>
       <c r="E78">
-        <v>-15.36790392472185</v>
+        <v>-15.66541561007778</v>
       </c>
       <c r="F78">
-        <v>-0.9644070151391649</v>
+        <v>-1.1782923069094</v>
       </c>
       <c r="G78">
-        <v>-5.726672209229194</v>
+        <v>-4.106573985948357</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.007001618334408</v>
       </c>
       <c r="E79">
-        <v>-15.47825377934076</v>
+        <v>-15.94699159540071</v>
       </c>
       <c r="F79">
-        <v>-1.130409357557977</v>
+        <v>-1.401004681723867</v>
       </c>
       <c r="G79">
-        <v>-5.021535941001049</v>
+        <v>-4.461391635756364</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.157963428672105</v>
       </c>
       <c r="E80">
-        <v>-16.52583020000915</v>
+        <v>-16.38267607967868</v>
       </c>
       <c r="F80">
-        <v>-1.305813669998565</v>
+        <v>-1.567534694178263</v>
       </c>
       <c r="G80">
-        <v>-5.879261874225281</v>
+        <v>-4.337395152582961</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.313226541408064</v>
       </c>
       <c r="E81">
-        <v>-17.43579082405845</v>
+        <v>-17.6895076372862</v>
       </c>
       <c r="F81">
-        <v>-1.448412148186083</v>
+        <v>-1.624537968634508</v>
       </c>
       <c r="G81">
-        <v>-5.317280216206301</v>
+        <v>-3.978217514299734</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.468482043069937</v>
       </c>
       <c r="E82">
-        <v>-16.2849833099112</v>
+        <v>-17.34339636887995</v>
       </c>
       <c r="F82">
-        <v>-1.27660129353884</v>
+        <v>-1.265427445642477</v>
       </c>
       <c r="G82">
-        <v>-4.760039259399557</v>
+        <v>-3.278245697112852</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.61785067363951</v>
       </c>
       <c r="E83">
-        <v>-16.89463818014184</v>
+        <v>-18.7615921592841</v>
       </c>
       <c r="F83">
-        <v>-1.664447881733985</v>
+        <v>-1.814504151648907</v>
       </c>
       <c r="G83">
-        <v>-6.487836150163965</v>
+        <v>-3.906868636837361</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.756992365792354</v>
       </c>
       <c r="E84">
-        <v>-20.73908618895359</v>
+        <v>-19.57642312985427</v>
       </c>
       <c r="F84">
-        <v>-2.155769155682428</v>
+        <v>-1.741036246694619</v>
       </c>
       <c r="G84">
-        <v>-6.026018357981173</v>
+        <v>-4.147422807357423</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.880924601375253</v>
       </c>
       <c r="E85">
-        <v>-19.85796288738514</v>
+        <v>-19.80628847048361</v>
       </c>
       <c r="F85">
-        <v>-1.887906615578374</v>
+        <v>-1.656154267297157</v>
       </c>
       <c r="G85">
-        <v>-5.566501394948175</v>
+        <v>-3.31023218811329</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.983790931887091</v>
       </c>
       <c r="E86">
-        <v>-22.20387091994865</v>
+        <v>-21.83197904901674</v>
       </c>
       <c r="F86">
-        <v>-2.07208996575383</v>
+        <v>-2.00311595395973</v>
       </c>
       <c r="G86">
-        <v>-4.571252089477078</v>
+        <v>-3.453492735779712</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.060064961474949</v>
       </c>
       <c r="E87">
-        <v>-22.78918071391405</v>
+        <v>-22.31629934413709</v>
       </c>
       <c r="F87">
-        <v>-2.093372381066555</v>
+        <v>-2.395554182668592</v>
       </c>
       <c r="G87">
-        <v>-6.189883741084018</v>
+        <v>-3.40943599574309</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.105425920689946</v>
       </c>
       <c r="E88">
-        <v>-23.90249246327779</v>
+        <v>-23.01614330270449</v>
       </c>
       <c r="F88">
-        <v>-2.011499860443463</v>
+        <v>-2.228807137954663</v>
       </c>
       <c r="G88">
-        <v>-6.108957455376534</v>
+        <v>-3.425359719786985</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.116425953673799</v>
       </c>
       <c r="E89">
-        <v>-24.9959513825919</v>
+        <v>-24.19311633966805</v>
       </c>
       <c r="F89">
-        <v>-2.26766336771778</v>
+        <v>-2.298843945126556</v>
       </c>
       <c r="G89">
-        <v>-5.168540715672385</v>
+        <v>-4.123576947838053</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.089819899611627</v>
       </c>
       <c r="E90">
-        <v>-26.25147985816652</v>
+        <v>-26.68506765897893</v>
       </c>
       <c r="F90">
-        <v>-2.229097894913046</v>
+        <v>-2.624191869515284</v>
       </c>
       <c r="G90">
-        <v>-4.975866965286802</v>
+        <v>-2.667754615306931</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.023870598708815</v>
       </c>
       <c r="E91">
-        <v>-26.2607994576743</v>
+        <v>-28.07863307925536</v>
       </c>
       <c r="F91">
-        <v>-1.888220566824035</v>
+        <v>-2.870623716541512</v>
       </c>
       <c r="G91">
-        <v>-4.740225644347019</v>
+        <v>-3.575910088730882</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.919027904587016</v>
       </c>
       <c r="E92">
-        <v>-28.98631135240479</v>
+        <v>-28.66841700554034</v>
       </c>
       <c r="F92">
-        <v>-2.414024290648813</v>
+        <v>-2.821179294635812</v>
       </c>
       <c r="G92">
-        <v>-6.337755878686644</v>
+        <v>-3.6718530090045</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.778134277617941</v>
       </c>
       <c r="E93">
-        <v>-31.5466426292315</v>
+        <v>-31.43267905235447</v>
       </c>
       <c r="F93">
-        <v>-2.560551715427809</v>
+        <v>-2.88061879762369</v>
       </c>
       <c r="G93">
-        <v>-5.128135507365581</v>
+        <v>-3.983355480976683</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.605686173557824</v>
       </c>
       <c r="E94">
-        <v>-32.15610730355381</v>
+        <v>-33.27279955876428</v>
       </c>
       <c r="F94">
-        <v>-2.422286427124335</v>
+        <v>-2.830098326461754</v>
       </c>
       <c r="G94">
-        <v>-6.237923067404382</v>
+        <v>-3.345860279206927</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.40796903706922</v>
       </c>
       <c r="E95">
-        <v>-34.23338172950832</v>
+        <v>-35.1301690226693</v>
       </c>
       <c r="F95">
-        <v>-2.902225932958313</v>
+        <v>-3.314437291572</v>
       </c>
       <c r="G95">
-        <v>-5.922524083332477</v>
+        <v>-4.03147426038999</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.194682186005982</v>
       </c>
       <c r="E96">
-        <v>-38.66075981919443</v>
+        <v>-36.94476025686086</v>
       </c>
       <c r="F96">
-        <v>-2.541170403304509</v>
+        <v>-3.365622941758384</v>
       </c>
       <c r="G96">
-        <v>-6.034172231644398</v>
+        <v>-4.227345997766508</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.9763744756645139</v>
       </c>
       <c r="E97">
-        <v>-39.16147771869655</v>
+        <v>-38.37568105922657</v>
       </c>
       <c r="F97">
-        <v>-3.006479284070242</v>
+        <v>-3.732359415060587</v>
       </c>
       <c r="G97">
-        <v>-5.924149561192259</v>
+        <v>-4.649069772923187</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.7635007167310496</v>
       </c>
       <c r="E98">
-        <v>-42.18946450629537</v>
+        <v>-40.26042514850796</v>
       </c>
       <c r="F98">
-        <v>-3.940914162593808</v>
+        <v>-3.685759606816101</v>
       </c>
       <c r="G98">
-        <v>-6.850261433621217</v>
+        <v>-4.854800314915655</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.5657500420257174</v>
       </c>
       <c r="E99">
-        <v>-43.04994928757387</v>
+        <v>-43.06642387601377</v>
       </c>
       <c r="F99">
-        <v>-3.603793480676492</v>
+        <v>-3.923204495889357</v>
       </c>
       <c r="G99">
-        <v>-7.209740331548518</v>
+        <v>-5.229454753594975</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.3937447282727266</v>
       </c>
       <c r="E100">
-        <v>-45.09838186257352</v>
+        <v>-44.76495032138875</v>
       </c>
       <c r="F100">
-        <v>-3.833328289420416</v>
+        <v>-4.466427957827605</v>
       </c>
       <c r="G100">
-        <v>-7.794975261435339</v>
+        <v>-5.745145053338327</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.2559414840865888</v>
       </c>
       <c r="E101">
-        <v>-47.41013614417118</v>
+        <v>-47.09661177472413</v>
       </c>
       <c r="F101">
-        <v>-3.658305025985117</v>
+        <v>-4.480063713645088</v>
       </c>
       <c r="G101">
-        <v>-7.316379624459521</v>
+        <v>-5.642379098708271</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.1566478639780553</v>
       </c>
       <c r="E102">
-        <v>-49.19014002601067</v>
+        <v>-48.92739003925612</v>
       </c>
       <c r="F102">
-        <v>-4.137727630559747</v>
+        <v>-4.551343900288582</v>
       </c>
       <c r="G102">
-        <v>-8.108480613458781</v>
+        <v>-6.64466000290478</v>
       </c>
     </row>
   </sheetData>
